--- a/Res_ConvLSTM/DroughtDataset_model_testing_1755521587_individual_h_11.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1755521587_individual_h_11.xlsx
@@ -658,7 +658,7 @@
         <v>0.05258738218505241</v>
       </c>
       <c r="C2" t="n">
-        <v>68340492</v>
+        <v>6212772</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>68340492</v>
+        <v>6212772</v>
       </c>
       <c r="K2" t="n">
-        <v>45713547</v>
+        <v>3611209</v>
       </c>
       <c r="L2" t="n">
-        <v>25156916</v>
+        <v>1715600</v>
       </c>
       <c r="M2" t="n">
-        <v>6234006</v>
+        <v>360406</v>
       </c>
       <c r="N2" t="n">
-        <v>334254</v>
+        <v>13436</v>
       </c>
       <c r="O2" t="n">
-        <v>3773154</v>
+        <v>229830</v>
       </c>
       <c r="P2" t="n">
-        <v>1568591</v>
+        <v>101665</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9998821020126343</v>
+        <v>0.9997767806053162</v>
       </c>
       <c r="R2" t="n">
-        <v>0.8440850973129272</v>
+        <v>0.7334116697311401</v>
       </c>
       <c r="S2" t="n">
-        <v>0.708891749382019</v>
+        <v>0.5318164825439453</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6068903207778931</v>
+        <v>0.3860352635383606</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4234982132911682</v>
+        <v>0.1880660057067871</v>
       </c>
       <c r="V2" t="n">
-        <v>0.6747346520423889</v>
+        <v>0.4522877037525177</v>
       </c>
       <c r="W2" t="n">
-        <v>0.7373631000518799</v>
+        <v>0.526042103767395</v>
       </c>
       <c r="X2" t="n">
-        <v>68340492</v>
+        <v>6212772</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,46 +742,46 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>68340492</v>
+        <v>6212772</v>
       </c>
       <c r="AF2" t="n">
-        <v>44488870</v>
+        <v>3557004</v>
       </c>
       <c r="AG2" t="n">
-        <v>23473597</v>
+        <v>1648362</v>
       </c>
       <c r="AH2" t="n">
-        <v>5649662</v>
+        <v>337891</v>
       </c>
       <c r="AI2" t="n">
-        <v>298959</v>
+        <v>12661</v>
       </c>
       <c r="AJ2" t="n">
-        <v>3480563</v>
+        <v>216237</v>
       </c>
       <c r="AK2" t="n">
-        <v>1471361</v>
+        <v>95469</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.8190881609916687</v>
+        <v>0.7203711271286011</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.6660129427909851</v>
+        <v>0.5144560933113098</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.5545850396156311</v>
+        <v>0.3648505210876465</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.3075209856033325</v>
+        <v>0.1432596296072006</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.6227976083755493</v>
+        <v>0.4256181418895721</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.6921143531799316</v>
+        <v>0.4939848780632019</v>
       </c>
     </row>
     <row r="3">
@@ -792,130 +792,130 @@
         <v>0.01618567928948078</v>
       </c>
       <c r="C3" t="n">
-        <v>2970</v>
+        <v>602</v>
       </c>
       <c r="D3" t="n">
-        <v>45713547</v>
+        <v>3611209</v>
       </c>
       <c r="E3" t="n">
-        <v>7337809</v>
+        <v>1081657</v>
       </c>
       <c r="F3" t="n">
-        <v>511820</v>
+        <v>98956</v>
       </c>
       <c r="G3" t="n">
-        <v>66892</v>
+        <v>10042</v>
       </c>
       <c r="H3" t="n">
-        <v>38435</v>
+        <v>11738</v>
       </c>
       <c r="I3" t="n">
-        <v>6606</v>
+        <v>2188</v>
       </c>
       <c r="J3" t="n">
-        <v>108425849</v>
+        <v>9856241</v>
       </c>
       <c r="K3" t="n">
-        <v>114652358</v>
+        <v>9941367</v>
       </c>
       <c r="L3" t="n">
-        <v>130673550</v>
+        <v>11255665</v>
       </c>
       <c r="M3" t="n">
-        <v>162467456</v>
+        <v>14555911</v>
       </c>
       <c r="N3" t="n">
-        <v>175341219</v>
+        <v>15922900</v>
       </c>
       <c r="O3" t="n">
-        <v>169345380</v>
+        <v>15279965</v>
       </c>
       <c r="P3" t="n">
-        <v>174087148</v>
+        <v>15784869</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.8516241312026978</v>
+        <v>0.7497747540473938</v>
       </c>
       <c r="S3" t="n">
-        <v>0.703294575214386</v>
+        <v>0.519184947013855</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6070761680603027</v>
+        <v>0.3828868269920349</v>
       </c>
       <c r="U3" t="n">
-        <v>0.341715008020401</v>
+        <v>0.1501346528530121</v>
       </c>
       <c r="V3" t="n">
-        <v>0.672562301158905</v>
+        <v>0.4487859308719635</v>
       </c>
       <c r="W3" t="n">
-        <v>0.7369310855865479</v>
+        <v>0.5242301225662231</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>44488870</v>
+        <v>3557004</v>
       </c>
       <c r="Z3" t="n">
-        <v>8374549</v>
+        <v>1114075</v>
       </c>
       <c r="AA3" t="n">
-        <v>582424</v>
+        <v>106809</v>
       </c>
       <c r="AB3" t="n">
-        <v>169979</v>
+        <v>20519</v>
       </c>
       <c r="AC3" t="n">
-        <v>53096</v>
+        <v>14993</v>
       </c>
       <c r="AD3" t="n">
-        <v>9161</v>
+        <v>2992</v>
       </c>
       <c r="AE3" t="n">
-        <v>108433908</v>
+        <v>9857628</v>
       </c>
       <c r="AF3" t="n">
-        <v>113270073</v>
+        <v>9873274</v>
       </c>
       <c r="AG3" t="n">
-        <v>129232943</v>
+        <v>11210265</v>
       </c>
       <c r="AH3" t="n">
-        <v>161967971</v>
+        <v>14540897</v>
       </c>
       <c r="AI3" t="n">
-        <v>175123035</v>
+        <v>15905190</v>
       </c>
       <c r="AJ3" t="n">
-        <v>169056251</v>
+        <v>15266468</v>
       </c>
       <c r="AK3" t="n">
-        <v>173991323</v>
+        <v>15778674</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.8288089036941528</v>
+        <v>0.7385204434394836</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.6562352180480957</v>
+        <v>0.4988369941711426</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.5501719117164612</v>
+        <v>0.3589674234390259</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.3056321740150452</v>
+        <v>0.1414747536182404</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.6204081773757935</v>
+        <v>0.422243058681488</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.6912519931793213</v>
+        <v>0.4922808110713959</v>
       </c>
     </row>
     <row r="4">
@@ -926,285 +926,285 @@
         <v>0.1032982568032969</v>
       </c>
       <c r="C4" t="n">
-        <v>1263</v>
+        <v>241</v>
       </c>
       <c r="D4" t="n">
-        <v>7819432</v>
+        <v>1179292</v>
       </c>
       <c r="E4" t="n">
-        <v>25156916</v>
+        <v>1715600</v>
       </c>
       <c r="F4" t="n">
-        <v>2294634</v>
+        <v>309195</v>
       </c>
       <c r="G4" t="n">
-        <v>101890</v>
+        <v>16177</v>
       </c>
       <c r="H4" t="n">
-        <v>344189</v>
+        <v>71087</v>
       </c>
       <c r="I4" t="n">
-        <v>51773</v>
+        <v>12818</v>
       </c>
       <c r="J4" t="n">
-        <v>8059</v>
+        <v>1387</v>
       </c>
       <c r="K4" t="n">
-        <v>8443963</v>
+        <v>1312641</v>
       </c>
       <c r="L4" t="n">
-        <v>10330753</v>
+        <v>1510325</v>
       </c>
       <c r="M4" t="n">
-        <v>4038041</v>
+        <v>573203</v>
       </c>
       <c r="N4" t="n">
-        <v>455015</v>
+        <v>58007</v>
       </c>
       <c r="O4" t="n">
-        <v>1818902</v>
+        <v>278320</v>
       </c>
       <c r="P4" t="n">
-        <v>558707</v>
+        <v>91599</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999410510063171</v>
+        <v>0.9998883605003357</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8478378653526306</v>
+        <v>0.7415029406547546</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7060820460319519</v>
+        <v>0.5254248380661011</v>
       </c>
       <c r="T4" t="n">
-        <v>0.6069832444190979</v>
+        <v>0.384454607963562</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3782362639904022</v>
+        <v>0.1669732183218002</v>
       </c>
       <c r="V4" t="n">
-        <v>0.6736467480659485</v>
+        <v>0.4505299925804138</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7371470332145691</v>
+        <v>0.5251345634460449</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>9045309</v>
+        <v>1226903</v>
       </c>
       <c r="Z4" t="n">
-        <v>23473597</v>
+        <v>1648362</v>
       </c>
       <c r="AA4" t="n">
-        <v>2587276</v>
+        <v>313588</v>
       </c>
       <c r="AB4" t="n">
-        <v>175500</v>
+        <v>22550</v>
       </c>
       <c r="AC4" t="n">
-        <v>422135</v>
+        <v>78235</v>
       </c>
       <c r="AD4" t="n">
-        <v>66280</v>
+        <v>14772</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>9826248</v>
+        <v>1380734</v>
       </c>
       <c r="AG4" t="n">
-        <v>11771360</v>
+        <v>1555725</v>
       </c>
       <c r="AH4" t="n">
-        <v>4537526</v>
+        <v>588217</v>
       </c>
       <c r="AI4" t="n">
-        <v>673199</v>
+        <v>75717</v>
       </c>
       <c r="AJ4" t="n">
-        <v>2108031</v>
+        <v>291817</v>
       </c>
       <c r="AK4" t="n">
-        <v>654532</v>
+        <v>97794</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.8239198923110962</v>
+        <v>0.7293328642845154</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.6610879302024841</v>
+        <v>0.5065262317657471</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.5523696541786194</v>
+        <v>0.3618850708007812</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.3065736591815948</v>
+        <v>0.1423616111278534</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.6216005682945251</v>
+        <v>0.4239239096641541</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.6916828751564026</v>
+        <v>0.4931313991546631</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>1342</v>
+        <v>235</v>
       </c>
       <c r="D5" t="n">
-        <v>443123</v>
+        <v>98733</v>
       </c>
       <c r="E5" t="n">
-        <v>2404545</v>
+        <v>315652</v>
       </c>
       <c r="F5" t="n">
-        <v>6234006</v>
+        <v>360406</v>
       </c>
       <c r="G5" t="n">
-        <v>157084</v>
+        <v>17448</v>
       </c>
       <c r="H5" t="n">
-        <v>901542</v>
+        <v>123850</v>
       </c>
       <c r="I5" t="n">
-        <v>127261</v>
+        <v>24962</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>7964532</v>
+        <v>1205183</v>
       </c>
       <c r="L5" t="n">
-        <v>10613181</v>
+        <v>1588810</v>
       </c>
       <c r="M5" t="n">
-        <v>4034897</v>
+        <v>580880</v>
       </c>
       <c r="N5" t="n">
-        <v>643912</v>
+        <v>76057</v>
       </c>
       <c r="O5" t="n">
-        <v>1836964</v>
+        <v>282285</v>
       </c>
       <c r="P5" t="n">
-        <v>559954</v>
+        <v>92267</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999544024467468</v>
+        <v>0.9999136924743652</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9071783423423767</v>
+        <v>0.8433253765106201</v>
       </c>
       <c r="S5" t="n">
-        <v>0.8815217018127441</v>
+        <v>0.8071525692939758</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9543319940567017</v>
+        <v>0.9281858205795288</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9937834739685059</v>
+        <v>0.9916577339172363</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9793190360069275</v>
+        <v>0.9651156663894653</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9936718344688416</v>
+        <v>0.9885587096214294</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>557886</v>
+        <v>113275</v>
       </c>
       <c r="Z5" t="n">
-        <v>2696336</v>
+        <v>318124</v>
       </c>
       <c r="AA5" t="n">
-        <v>5649662</v>
+        <v>337891</v>
       </c>
       <c r="AB5" t="n">
-        <v>183791</v>
+        <v>18281</v>
       </c>
       <c r="AC5" t="n">
-        <v>1027269</v>
+        <v>126497</v>
       </c>
       <c r="AD5" t="n">
-        <v>153959</v>
+        <v>27218</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>9189209</v>
+        <v>1259388</v>
       </c>
       <c r="AG5" t="n">
-        <v>12296500</v>
+        <v>1656048</v>
       </c>
       <c r="AH5" t="n">
-        <v>4619241</v>
+        <v>603395</v>
       </c>
       <c r="AI5" t="n">
-        <v>679207</v>
+        <v>76832</v>
       </c>
       <c r="AJ5" t="n">
-        <v>2129555</v>
+        <v>295878</v>
       </c>
       <c r="AK5" t="n">
-        <v>657184</v>
+        <v>98463</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.8924309611320496</v>
+        <v>0.8357152342796326</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.8638498783111572</v>
+        <v>0.8001435399055481</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9482008218765259</v>
+        <v>0.925850510597229</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9923495650291443</v>
+        <v>0.9905074834823608</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9760282635688782</v>
+        <v>0.9634299874305725</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9925796985626221</v>
+        <v>0.987787663936615</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>1698</v>
+        <v>209</v>
       </c>
       <c r="D6" t="n">
-        <v>135190</v>
+        <v>18446</v>
       </c>
       <c r="E6" t="n">
-        <v>171075</v>
+        <v>23324</v>
       </c>
       <c r="F6" t="n">
-        <v>201099</v>
+        <v>18088</v>
       </c>
       <c r="G6" t="n">
-        <v>334254</v>
+        <v>13436</v>
       </c>
       <c r="H6" t="n">
-        <v>113907</v>
+        <v>12817</v>
       </c>
       <c r="I6" t="n">
-        <v>20943</v>
+        <v>3173</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>155149</v>
+        <v>19464</v>
       </c>
       <c r="Z6" t="n">
-        <v>185421</v>
+        <v>23674</v>
       </c>
       <c r="AA6" t="n">
-        <v>188617</v>
+        <v>17518</v>
       </c>
       <c r="AB6" t="n">
-        <v>298959</v>
+        <v>12661</v>
       </c>
       <c r="AC6" t="n">
-        <v>126226</v>
+        <v>12841</v>
       </c>
       <c r="AD6" t="n">
-        <v>23794</v>
+        <v>3335</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>534</v>
+        <v>72</v>
       </c>
       <c r="D7" t="n">
-        <v>43700</v>
+        <v>14932</v>
       </c>
       <c r="E7" t="n">
-        <v>378621</v>
+        <v>79496</v>
       </c>
       <c r="F7" t="n">
-        <v>949327</v>
+        <v>128020</v>
       </c>
       <c r="G7" t="n">
-        <v>112658</v>
+        <v>11307</v>
       </c>
       <c r="H7" t="n">
-        <v>3773154</v>
+        <v>229830</v>
       </c>
       <c r="I7" t="n">
-        <v>352124</v>
+        <v>48458</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>63239</v>
+        <v>19084</v>
       </c>
       <c r="Z7" t="n">
-        <v>464812</v>
+        <v>87959</v>
       </c>
       <c r="AA7" t="n">
-        <v>1076157</v>
+        <v>128273</v>
       </c>
       <c r="AB7" t="n">
-        <v>124009</v>
+        <v>11085</v>
       </c>
       <c r="AC7" t="n">
-        <v>3480563</v>
+        <v>216237</v>
       </c>
       <c r="AD7" t="n">
-        <v>401338</v>
+        <v>49477</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>252</v>
+        <v>28</v>
       </c>
       <c r="D8" t="n">
-        <v>2518</v>
+        <v>1238</v>
       </c>
       <c r="E8" t="n">
-        <v>38703</v>
+        <v>10196</v>
       </c>
       <c r="F8" t="n">
-        <v>81161</v>
+        <v>18944</v>
       </c>
       <c r="G8" t="n">
-        <v>16491</v>
+        <v>3033</v>
       </c>
       <c r="H8" t="n">
-        <v>420829</v>
+        <v>58828</v>
       </c>
       <c r="I8" t="n">
-        <v>1568591</v>
+        <v>101665</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>4665</v>
+        <v>2008</v>
       </c>
       <c r="Z8" t="n">
-        <v>50242</v>
+        <v>11893</v>
       </c>
       <c r="AA8" t="n">
-        <v>103052</v>
+        <v>22029</v>
       </c>
       <c r="AB8" t="n">
-        <v>19920</v>
+        <v>3282</v>
       </c>
       <c r="AC8" t="n">
-        <v>479305</v>
+        <v>59251</v>
       </c>
       <c r="AD8" t="n">
-        <v>1471361</v>
+        <v>95469</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
